--- a/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
+++ b/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>

--- a/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
+++ b/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
@@ -34,7 +34,7 @@
     <t xml:space="preserve">NOM et prénom : Mendil  Hamza</t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
+    <t xml:space="preserve">N° candidat : 2217580300</t>
   </si>
   <si>
     <t xml:space="preserve">Centre de formation : Lycée Turgot</t>

--- a/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
+++ b/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="57">
   <si>
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -190,13 +190,7 @@
     <t xml:space="preserve">Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t xml:space="preserve">Création d’un MCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2025 au 19/05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Création d’un MCV en poo</t>
+    <t xml:space="preserve">Création d’un MCV en poo pour une entreprise</t>
   </si>
   <si>
     <t xml:space="preserve">19/05/2025 au 06/07/2025</t>
@@ -1375,9 +1369,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
-        <v>28</v>
-      </c>
+      <c r="E12" s="21"/>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
       <c r="H12" s="22"/>
@@ -1407,11 +1399,11 @@
       <c r="B13" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21" t="s">
+      <c r="C13" s="21" t="s">
         <v>28</v>
       </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
       <c r="H13" s="22"/>
@@ -1653,9 +1645,13 @@
       <c r="B20" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="E20" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="22"/>
@@ -1678,23 +1674,17 @@
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
     </row>
-    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="24" t="s">
+    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="22"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -1714,17 +1704,23 @@
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
     </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
-        <v>48</v>
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>47</v>
       </c>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
+      <c r="B22" s="20" t="n">
+        <v>46036</v>
+      </c>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="22"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -1746,15 +1742,15 @@
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>46036</v>
-      </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21" t="s">
+      <c r="C23" s="21" t="s">
         <v>28</v>
       </c>
+      <c r="D23" s="21"/>
       <c r="E23" s="21"/>
       <c r="F23" s="21"/>
       <c r="G23" s="21" t="s">
@@ -1784,18 +1780,18 @@
       <c r="A24" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="24" t="s">
-        <v>51</v>
+      <c r="B24" s="20" t="n">
+        <v>46037</v>
       </c>
       <c r="C24" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D24" s="21"/>
+      <c r="D24" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="E24" s="21"/>
       <c r="F24" s="21"/>
-      <c r="G24" s="21" t="s">
-        <v>26</v>
-      </c>
+      <c r="G24" s="21"/>
       <c r="H24" s="22"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -1818,20 +1814,20 @@
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="24" t="s">
         <v>52</v>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>46037</v>
       </c>
       <c r="C25" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>28</v>
-      </c>
+      <c r="D25" s="21"/>
       <c r="E25" s="21"/>
       <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
+      <c r="G25" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="H25" s="22"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -1862,12 +1858,12 @@
       <c r="C26" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="21"/>
+      <c r="D26" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="E26" s="21"/>
       <c r="F26" s="21"/>
-      <c r="G26" s="21" t="s">
-        <v>26</v>
-      </c>
+      <c r="G26" s="21"/>
       <c r="H26" s="22"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -1895,15 +1891,15 @@
       <c r="B27" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="C27" s="21" t="s">
-        <v>28</v>
-      </c>
+      <c r="C27" s="21"/>
       <c r="D27" s="21" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
+      <c r="G27" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="H27" s="22"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
@@ -1924,41 +1920,33 @@
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
     </row>
-    <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="22"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6"/>
-      <c r="Y28" s="6"/>
-      <c r="Z28" s="6"/>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6"/>
@@ -28980,34 +28968,7 @@
       <c r="Y993" s="3"/>
       <c r="Z993" s="3"/>
     </row>
-    <row r="994" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A994" s="6"/>
-      <c r="B994" s="6"/>
-      <c r="C994" s="6"/>
-      <c r="D994" s="6"/>
-      <c r="E994" s="6"/>
-      <c r="F994" s="6"/>
-      <c r="G994" s="6"/>
-      <c r="H994" s="6"/>
-      <c r="I994" s="3"/>
-      <c r="J994" s="3"/>
-      <c r="K994" s="3"/>
-      <c r="L994" s="3"/>
-      <c r="M994" s="3"/>
-      <c r="N994" s="3"/>
-      <c r="O994" s="3"/>
-      <c r="P994" s="3"/>
-      <c r="Q994" s="3"/>
-      <c r="R994" s="3"/>
-      <c r="S994" s="3"/>
-      <c r="T994" s="3"/>
-      <c r="U994" s="3"/>
-      <c r="V994" s="3"/>
-      <c r="W994" s="3"/>
-      <c r="X994" s="3"/>
-      <c r="Y994" s="3"/>
-      <c r="Z994" s="3"/>
-    </row>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -29027,7 +28988,7 @@
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://hmz75015.github.io"/>

--- a/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
+++ b/fichier/8 - BTS SIO - Annexe 8-1 - Tableau de synthese - Epreuve E5 hamza - 2025.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">SESSION 2025</t>
+    <t xml:space="preserve">SESSION 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
